--- a/processed_ruby_restored_xlsx/sc103_最終決定.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc103_最終決定.ss.xlsx
@@ -560,8 +560,8 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>I turned my attention to the hallway, but there was no
-sign of anyone.</t>
+          <t>I turned my attention to the hallway, but there was
+no sign of anyone.</t>
         </is>
       </c>
       <c r="C7" t="n">
